--- a/docs/d/227/inyear.xlsx
+++ b/docs/d/227/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 65 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 64 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA152"/>
+  <dimension ref="A1:AA153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>4</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>7</v>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3028,11 +3028,11 @@
       <c r="U24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>3</v>
+      <c r="V24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>7</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3322,8 +3322,8 @@
       <c r="V27" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W27" s="9" t="n">
-        <v>3</v>
+      <c r="W27" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>7</v>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -9525,7 +9525,7 @@
         <v>1</v>
       </c>
       <c r="U91" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V91" s="9" t="n">
         <v>0</v>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10315,8 +10315,8 @@
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10479,11 +10479,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P101" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="9" t="n">
-        <v>1</v>
+      <c r="P101" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
@@ -10819,15 +10819,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>28678996</v>
+        <v>28680911</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Paychex Catalyst Crew 1</t>
+          <t>Paychex Catalyst Crew</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,25 +10841,25 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K105" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L105" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N105" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O105" s="7" t="inlineStr">
@@ -10897,11 +10897,11 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA105" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -10916,15 +10916,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>7908984</v>
+        <v>28678996</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>RCB Griffin</t>
+          <t>Paychex Catalyst Crew 1</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10938,25 +10938,25 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K106" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N106" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O106" s="7" t="inlineStr">
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q106" s="9" t="n">
         <v>0</v>
@@ -10973,14 +10973,14 @@
       <c r="R106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S106" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T106" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U106" s="10" t="n">
-        <v>2</v>
+      <c r="S106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
         <v>0</v>
@@ -10988,17 +10988,17 @@
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="10" t="n">
-        <v>7</v>
+      <c r="X106" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA106" s="10" t="n">
-        <v>1</v>
+      <c r="Z106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -11013,15 +11013,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>7908988</v>
+        <v>7908984</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>RCB Pegasus</t>
+          <t>RCB Griffin</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11062,22 +11062,22 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q107" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="T107" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U107" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V107" s="9" t="n">
         <v>0</v>
@@ -11110,15 +11110,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>7908991</v>
+        <v>7908988</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>RCB Phoenix</t>
+          <t>RCB Pegasus</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,25 +11132,25 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K108" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L108" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O108" s="7" t="inlineStr">
@@ -11159,22 +11159,22 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T108" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V108" s="9" t="n">
         <v>0</v>
@@ -11182,17 +11182,17 @@
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X108" s="9" t="n">
-        <v>0</v>
+      <c r="X108" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA108" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -11203,19 +11203,19 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28675609</v>
+        <v>7908991</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Greenage Toastmasters Club</t>
+          <t>RCB Phoenix</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11229,25 +11229,25 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O109" s="7" t="inlineStr">
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -11274,22 +11274,22 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X109" s="10" t="n">
-        <v>5</v>
+      <c r="X109" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA109" s="10" t="n">
-        <v>1</v>
+      <c r="Z109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -11304,15 +11304,15 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>5843852</v>
+        <v>28675609</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>HSR Toastmasters Club</t>
+          <t>Greenage Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11355,29 +11355,29 @@
       <c r="P110" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q110" s="10" t="n">
+      <c r="Q110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V110" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="W110" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X110" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -11401,15 +11401,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>9688</v>
+        <v>5843852</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Infosys Toastmasters, Bangalore</t>
+          <t>HSR Toastmasters Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11452,8 +11452,8 @@
       <c r="P111" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q111" s="9" t="n">
-        <v>0</v>
+      <c r="Q111" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
@@ -11461,8 +11461,8 @@
       <c r="S111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
@@ -11471,7 +11471,7 @@
         <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>7</v>
@@ -11498,11 +11498,11 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>7586759</v>
+        <v>9688</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>MOOG Flyers</t>
+          <t>Infosys Toastmasters, Bangalore</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
@@ -11523,10 +11523,10 @@
         <v>29</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -11558,20 +11558,20 @@
       <c r="S112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T112" s="10" t="n">
-        <v>1</v>
+      <c r="T112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>0</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X112" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -11595,15 +11595,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>7959873</v>
+        <v>7586759</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Wipro House of Speakers</t>
+          <t>MOOG Flyers</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11617,17 +11617,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L113" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -11652,29 +11652,29 @@
       <c r="R113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S113" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T113" s="9" t="n">
-        <v>0</v>
+      <c r="S113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -11683,24 +11683,24 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>28679896</v>
+        <v>7959873</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Chilli Champions Toastmasters Club</t>
+          <t>Wipro House of Speakers</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11714,17 +11714,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -11741,7 +11741,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -11749,8 +11749,8 @@
       <c r="R114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S114" s="9" t="n">
-        <v>0</v>
+      <c r="S114" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T114" s="9" t="n">
         <v>0</v>
@@ -11759,13 +11759,13 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X114" s="9" t="n">
-        <v>0</v>
+      <c r="X114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -11789,15 +11789,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>4184180</v>
+        <v>28679896</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Deshpande Educational Trust Toastmasters Club</t>
+          <t>Chilli Champions Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>0</v>
@@ -11856,19 +11856,19 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X115" s="10" t="n">
-        <v>6</v>
+      <c r="X115" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="10" t="n">
-        <v>1</v>
+      <c r="Z115" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -11886,39 +11886,39 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>28678921</v>
+        <v>4184180</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>InfyHubliVox Toastmasters Club</t>
+          <t>Deshpande Educational Trust Toastmasters Club</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J116" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K116" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F116" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G116" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I116" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J116" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -11937,35 +11937,35 @@
       <c r="P116" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" s="10" t="n">
-        <v>2</v>
+      <c r="Q116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T116" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U116" s="10" t="n">
-        <v>2</v>
+      <c r="T116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -11983,15 +11983,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>6988591</v>
+        <v>28678921</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>SDMCET Toastmasters Club</t>
+          <t>InfyHubliVox Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,10 +12005,10 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K117" s="4" t="n">
         <v>0</v>
@@ -12032,22 +12032,22 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q117" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" s="9" t="n">
-        <v>0</v>
+      <c r="T117" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U117" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V117" s="9" t="n">
         <v>0</v>
@@ -12080,15 +12080,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>7712481</v>
+        <v>6988591</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters For Hubballi Entrepreneurs</t>
+          <t>SDMCET Toastmasters Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,17 +12102,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12129,16 +12129,16 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q118" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T118" s="9" t="n">
         <v>0</v>
@@ -12146,20 +12146,20 @@
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="10" t="n">
+      <c r="V118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W118" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X118" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="10" t="n">
-        <v>1</v>
+      <c r="Z118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -12173,19 +12173,19 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28675688</v>
+        <v>7712481</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>APS Toastmasters Club</t>
+          <t>Toastmasters For Hubballi Entrepreneurs</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12226,10 +12226,10 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q119" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q119" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
@@ -12237,20 +12237,20 @@
       <c r="S119" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T119" s="10" t="n">
-        <v>1</v>
+      <c r="T119" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V119" s="9" t="n">
+      <c r="V119" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W119" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="W119" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X119" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -12274,15 +12274,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>28677946</v>
+        <v>28675688</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Belagavi Toastmasters Centenary Club</t>
+          <t>APS Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -12323,31 +12323,31 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q120" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q120" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T120" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U120" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V120" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="W120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -12371,15 +12371,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>7826939</v>
+        <v>28677946</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Kannada English Bilingual Toastmasters Club</t>
+          <t>Belagavi Toastmasters Centenary Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12393,17 +12393,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -12420,11 +12420,11 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q121" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q121" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
       </c>
@@ -12434,17 +12434,17 @@
       <c r="T121" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="9" t="n">
-        <v>0</v>
+      <c r="U121" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -12468,11 +12468,11 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>6997339</v>
+        <v>7826939</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>KLS IMER Toastmasters</t>
+          <t>Kannada English Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -12490,17 +12490,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="8" t="n">
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
@@ -12528,17 +12528,17 @@
       <c r="S122" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T122" s="9" t="n">
-        <v>0</v>
+      <c r="T122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="10" t="n">
-        <v>4</v>
+      <c r="V122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W122" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X122" s="10" t="n">
         <v>5</v>
@@ -12565,15 +12565,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>7335393</v>
+        <v>6997339</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Shivamogga Toastmasters</t>
+          <t>KLS IMER Toastmasters</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,25 +12587,25 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O123" s="7" t="inlineStr">
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -12623,7 +12623,7 @@
         <v>0</v>
       </c>
       <c r="S123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T123" s="9" t="n">
         <v>0</v>
@@ -12631,23 +12631,23 @@
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>0</v>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X123" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA123" s="9" t="n">
-        <v>0</v>
+      <c r="Z123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA123" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -12662,11 +12662,11 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28680663</v>
+        <v>7335393</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>SPS Toastmasters Club</t>
+          <t>Shivamogga Toastmasters</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
@@ -12684,25 +12684,25 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="K124" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O124" s="7" t="inlineStr">
@@ -12734,8 +12734,8 @@
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="10" t="n">
-        <v>7</v>
+      <c r="X124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -12743,8 +12743,8 @@
       <c r="Z124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA124" s="10" t="n">
-        <v>1</v>
+      <c r="AA124" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -12755,19 +12755,19 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>1214543</v>
+        <v>28680663</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>GOA Toastmasters Club</t>
+          <t>SPS Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,10 +12781,10 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K125" s="4" t="n">
         <v>0</v>
@@ -12808,16 +12808,16 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T125" s="9" t="n">
         <v>0</v>
@@ -12837,8 +12837,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="10" t="n">
-        <v>1</v>
+      <c r="Z125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -12856,11 +12856,11 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>3214306</v>
+        <v>1214543</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>International Centre GOA (ICG) Toastmasters Club</t>
+          <t>GOA Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -12905,16 +12905,16 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" s="9" t="n">
         <v>0</v>
@@ -12923,13 +12923,13 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -12953,11 +12953,11 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>28676711</v>
+        <v>3214306</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Melange Toastmasters Club</t>
+          <t>International Centre GOA (ICG) Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
@@ -12975,17 +12975,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L127" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13005,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13020,13 +13020,13 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X127" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13050,11 +13050,11 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>7946347</v>
+        <v>28676711</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>TheanTamil Toastmasters Club</t>
+          <t>Melange Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>0</v>
       </c>
       <c r="Q128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R128" s="9" t="n">
         <v>0</v>
@@ -13117,13 +13117,13 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X128" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
@@ -13147,11 +13147,11 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>2575847</v>
+        <v>7946347</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters International Margao</t>
+          <t>TheanTamil Toastmasters Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13214,13 +13214,13 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X129" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -13240,15 +13240,15 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>28678487</v>
+        <v>2575847</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Calangute Toastmasters Club</t>
+          <t>Toastmasters International Margao</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
@@ -13266,17 +13266,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q130" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R130" s="9" t="n">
         <v>0</v>
@@ -13311,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -13341,11 +13341,11 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>4361333</v>
+        <v>28678487</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Mapusa Toastmasters</t>
+          <t>Calangute Toastmasters Club</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -13363,17 +13363,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L131" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M131" s="8" t="n">
@@ -13390,37 +13390,37 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S131" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T131" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X131" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -13438,15 +13438,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>7856600</v>
+        <v>4361333</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Online Toastmasters Tribe</t>
+          <t>Mapusa Toastmasters</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13496,16 +13496,16 @@
         <v>0</v>
       </c>
       <c r="S132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -13535,11 +13535,11 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>6941455</v>
+        <v>7856600</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Tangentia Toastmasters</t>
+          <t>Online Toastmasters Tribe</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
@@ -13557,10 +13557,10 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K133" s="4" t="n">
         <v>0</v>
@@ -13608,7 +13608,7 @@
         <v>0</v>
       </c>
       <c r="X133" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
@@ -13623,24 +13623,24 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>632425</v>
+        <v>6941455</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>CMS Speakers Forum Toastmasters Club</t>
+          <t>Tangentia Toastmasters</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -13681,31 +13681,31 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q134" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q134" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R134" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S134" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U134" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="S134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X134" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -13729,15 +13729,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>725960</v>
+        <v>632425</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Jain Toastmasters Club</t>
+          <t>CMS Speakers Forum Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13778,22 +13778,22 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q135" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S135" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U135" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="T135" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U135" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
         <v>2</v>
@@ -13826,11 +13826,11 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>726698</v>
+        <v>725960</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Mahaveer Toastmasters Club</t>
+          <t>Jain Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -13875,16 +13875,16 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q136" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R136" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S136" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T136" s="10" t="n">
         <v>1</v>
@@ -13893,7 +13893,7 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -13923,15 +13923,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>726395</v>
+        <v>726698</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>SBMJC Toastmasters Club</t>
+          <t>Mahaveer Toastmasters Club</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -13971,26 +13971,26 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P137" s="10" t="n">
-        <v>5</v>
+      <c r="P137" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Q137" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R137" s="10" t="n">
+      <c r="R137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S137" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="S137" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="T137" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U137" s="10" t="n">
-        <v>2</v>
+      <c r="U137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
@@ -14016,19 +14016,19 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>6636162</v>
+        <v>726395</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>BTM Toastmasters Club</t>
+          <t>SBMJC Toastmasters Club</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,17 +14042,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="8" t="n">
@@ -14068,29 +14068,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P138" s="9" t="n">
-        <v>2</v>
+      <c r="P138" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q138" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R138" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" s="9" t="n">
-        <v>1</v>
+      <c r="R138" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S138" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="T138" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U138" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W138" s="10" t="n">
-        <v>4</v>
+      <c r="U138" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V138" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X138" s="10" t="n">
         <v>7</v>
@@ -14098,8 +14098,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="10" t="n">
-        <v>1</v>
+      <c r="Z138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14117,15 +14117,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>28678910</v>
+        <v>6636162</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Furlenco Toastmasters Club</t>
+          <t>BTM Toastmasters Club</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14139,17 +14139,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -14166,37 +14166,37 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q139" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R139" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" s="9" t="n">
-        <v>2</v>
+      <c r="V139" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W139" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X139" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -14214,15 +14214,15 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>6831114</v>
+        <v>28678910</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Leaders Speak</t>
+          <t>Furlenco Toastmasters Club</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,17 +14236,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K140" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M140" s="8" t="n">
@@ -14263,7 +14263,7 @@
         </is>
       </c>
       <c r="P140" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q140" s="9" t="n">
         <v>0</v>
@@ -14274,8 +14274,8 @@
       <c r="S140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T140" s="10" t="n">
-        <v>1</v>
+      <c r="T140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U140" s="9" t="n">
         <v>0</v>
@@ -14286,14 +14286,14 @@
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X140" s="10" t="n">
-        <v>6</v>
+      <c r="X140" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="10" t="n">
-        <v>1</v>
+      <c r="Z140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -14311,15 +14311,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>2405453</v>
+        <v>6831114</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>vTalk Toastmasters Club</t>
+          <t>Leaders Speak</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14333,17 +14333,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L141" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L141" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M141" s="8" t="n">
@@ -14360,7 +14360,7 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q141" s="9" t="n">
         <v>0</v>
@@ -14371,26 +14371,26 @@
       <c r="S141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T141" s="9" t="n">
-        <v>0</v>
+      <c r="T141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X141" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -14408,39 +14408,39 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>28678951</v>
+        <v>2405453</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Welldoc Toastmasters</t>
+          <t>vTalk Toastmasters Club</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G142" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J142" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K142" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F142" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G142" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H142" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I142" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="J142" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K142" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L142" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M142" s="8" t="n">
@@ -14474,20 +14474,20 @@
       <c r="U142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V142" s="10" t="n">
+      <c r="V142" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W142" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W142" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X142" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="10" t="n">
-        <v>1</v>
+      <c r="Z142" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -14501,19 +14501,19 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>7762021</v>
+        <v>28678951</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Christ Toastmasters Club</t>
+          <t>Welldoc Toastmasters</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -14530,10 +14530,10 @@
         <v>23</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -14565,8 +14565,8 @@
       <c r="S143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T143" s="10" t="n">
-        <v>1</v>
+      <c r="T143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U143" s="9" t="n">
         <v>0</v>
@@ -14575,7 +14575,7 @@
         <v>4</v>
       </c>
       <c r="W143" s="10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X143" s="10" t="n">
         <v>7</v>
@@ -14602,15 +14602,15 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>28678938</v>
+        <v>7762021</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>DSBA Toastmaster Club</t>
+          <t>Christ Toastmasters Club</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
@@ -14662,17 +14662,17 @@
       <c r="S144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T144" s="9" t="n">
-        <v>0</v>
+      <c r="T144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W144" s="9" t="n">
-        <v>0</v>
+      <c r="V144" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W144" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>7</v>
@@ -14680,8 +14680,8 @@
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA144" s="10" t="n">
         <v>1</v>
@@ -14699,15 +14699,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>28679826</v>
+        <v>28678938</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>DSBA Toastmasters Legacy Club</t>
+          <t>DSBA Toastmaster Club</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,10 +14721,10 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="K145" s="4" t="n">
         <v>0</v>
@@ -14747,8 +14747,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P145" s="9" t="n">
-        <v>0</v>
+      <c r="P145" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q145" s="9" t="n">
         <v>0</v>
@@ -14796,11 +14796,11 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>28676701</v>
+        <v>28679826</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Evolve Toastmasters</t>
+          <t>DSBA Toastmasters Legacy Club</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
@@ -14818,10 +14818,10 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K146" s="4" t="n">
         <v>0</v>
@@ -14893,15 +14893,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>7711039</v>
+        <v>28676701</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Words Worth Toastmasters</t>
+          <t>Evolve Toastmasters</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         </is>
       </c>
       <c r="P147" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q147" s="9" t="n">
         <v>0</v>
@@ -14950,8 +14950,8 @@
       <c r="R147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S147" s="10" t="n">
-        <v>2</v>
+      <c r="S147" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T147" s="9" t="n">
         <v>0</v>
@@ -14959,11 +14959,11 @@
       <c r="U147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V147" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W147" s="10" t="n">
-        <v>10</v>
+      <c r="V147" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X147" s="10" t="n">
         <v>7</v>
@@ -14971,8 +14971,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="10" t="n">
-        <v>1</v>
+      <c r="Z147" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -14986,19 +14986,19 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>7992645</v>
+        <v>7711039</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>All Women and Entrepreneurs Toastmasters Club</t>
+          <t>Words Worth Toastmasters</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         </is>
       </c>
       <c r="P148" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q148" s="9" t="n">
         <v>0</v>
@@ -15047,8 +15047,8 @@
       <c r="R148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S148" s="9" t="n">
-        <v>0</v>
+      <c r="S148" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T148" s="9" t="n">
         <v>0</v>
@@ -15056,20 +15056,20 @@
       <c r="U148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W148" s="9" t="n">
-        <v>0</v>
+      <c r="V148" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W148" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X148" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="9" t="n">
-        <v>0</v>
+      <c r="Z148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA148" s="10" t="n">
         <v>1</v>
@@ -15087,15 +15087,15 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>5953659</v>
+        <v>7992645</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Ritoras</t>
+          <t>All Women and Entrepreneurs Toastmasters Club</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -15139,13 +15139,13 @@
         <v>0</v>
       </c>
       <c r="Q149" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R149" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S149" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T149" s="9" t="n">
         <v>0</v>
@@ -15154,19 +15154,19 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X149" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="10" t="n">
-        <v>1</v>
+      <c r="Z149" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA149" s="10" t="n">
         <v>1</v>
@@ -15184,15 +15184,15 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>28675687</v>
+        <v>5953659</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>School of Commerce, Jain University Toastmasters</t>
+          <t>Ritoras</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15233,28 +15233,28 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W150" s="10" t="n">
-        <v>6</v>
+      <c r="W150" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>7</v>
@@ -15281,15 +15281,15 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>7934414</v>
+        <v>28675687</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>SpeakEasy Advanced Toastmasters</t>
+          <t>School of Commerce, Jain University Toastmasters</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
@@ -15330,10 +15330,10 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>0</v>
@@ -15341,26 +15341,26 @@
       <c r="S151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T151" s="10" t="n">
-        <v>1</v>
+      <c r="T151" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V151" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W151" s="9" t="n">
-        <v>0</v>
+      <c r="V151" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W151" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X151" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="9" t="n">
-        <v>0</v>
+      <c r="Z151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA151" s="10" t="n">
         <v>1</v>
@@ -15378,15 +15378,15 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>28677183</v>
+        <v>7934414</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Titans Toastmasters Club</t>
+          <t>SpeakEasy Advanced Toastmasters</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J152" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="J152" s="4" t="n">
-        <v>13</v>
-      </c>
       <c r="K152" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -15438,33 +15438,130 @@
       <c r="S152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T152" s="9" t="n">
-        <v>0</v>
+      <c r="T152" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V152" s="10" t="n">
+      <c r="V152" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W152" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W152" s="9" t="n">
+      <c r="Y152" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA152" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="n">
+        <v>28677183</v>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>Titans Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G153" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J153" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K153" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M153" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O153" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W153" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="X152" s="10" t="n">
+      <c r="X153" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Y152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z152" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA152" s="10" t="n">
+      <c r="Y153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA153" s="10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA152"/>
+  <autoFilter ref="A1:AA153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15650,7 +15747,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15683,13 +15780,13 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -16112,13 +16209,13 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -16142,16 +16239,16 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
         <v>6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -16160,7 +16257,7 @@
         <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -16409,7 +16506,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/227/inyear.xlsx
+++ b/docs/d/227/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/227/inyear.xlsx
+++ b/docs/d/227/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 64 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 64 clubs short</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1273,8 +1273,8 @@
       <c r="R6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="9" t="n">
-        <v>1</v>
+      <c r="S6" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T6" s="10" t="n">
         <v>1</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1470,8 +1470,8 @@
       <c r="S8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="9" t="n">
-        <v>0</v>
+      <c r="T8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U8" s="9" t="n">
         <v>0</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1761,8 +1761,8 @@
       <c r="S11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="9" t="n">
-        <v>0</v>
+      <c r="T11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U11" s="9" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1944,22 +1944,22 @@
         </is>
       </c>
       <c r="P13" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="Q13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" s="10" t="n">
-        <v>3</v>
       </c>
       <c r="V13" s="10" t="n">
         <v>4</v>
@@ -2729,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" s="10" t="n">
         <v>1</v>
@@ -3305,7 +3305,7 @@
         <v>4</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="P49" s="10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q49" s="10" t="n">
         <v>2</v>
@@ -5447,8 +5447,8 @@
       <c r="S49" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T49" s="9" t="n">
-        <v>0</v>
+      <c r="T49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U49" s="9" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6409,7 +6409,7 @@
         <v>4</v>
       </c>
       <c r="Q59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" s="9" t="n">
         <v>0</v>
@@ -6420,8 +6420,8 @@
       <c r="T59" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U59" s="9" t="n">
-        <v>0</v>
+      <c r="U59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V59" s="9" t="n">
         <v>0</v>
@@ -6706,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="10" t="n">
         <v>1</v>
@@ -6894,7 +6894,7 @@
         <v>2</v>
       </c>
       <c r="Q64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="P70" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q70" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="Q70" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R70" s="9" t="n">
         <v>0</v>
@@ -8249,7 +8249,7 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q78" s="9" t="n">
         <v>0</v>
@@ -10286,7 +10286,7 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q99" s="9" t="n">
         <v>1</v>
@@ -11062,10 +11062,10 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
@@ -11077,7 +11077,7 @@
         <v>1</v>
       </c>
       <c r="U107" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V107" s="9" t="n">
         <v>0</v>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12246,8 +12246,8 @@
       <c r="V119" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W119" s="9" t="n">
-        <v>3</v>
+      <c r="W119" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X119" s="10" t="n">
         <v>7</v>
@@ -13002,10 +13002,10 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -14845,7 +14845,7 @@
         </is>
       </c>
       <c r="P146" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q146" s="9" t="n">
         <v>0</v>
@@ -15042,7 +15042,7 @@
         <v>3</v>
       </c>
       <c r="Q148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
@@ -15648,7 +15648,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15714,7 +15714,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -15879,7 +15879,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15945,7 +15945,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -16044,7 +16044,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16308,7 +16308,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>

--- a/docs/d/227/inyear.xlsx
+++ b/docs/d/227/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$155</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 64 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 50 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA153"/>
+  <dimension ref="A1:AA155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="9" t="n">
         <v>0</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1458,8 +1458,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P8" s="9" t="n">
-        <v>3</v>
+      <c r="P8" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q8" s="10" t="n">
         <v>2</v>
@@ -1653,16 +1653,16 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="9" t="n">
         <v>0</v>
@@ -1959,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V13" s="10" t="n">
         <v>4</v>
@@ -2283,15 +2283,15 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>28679257</v>
+        <v>28675371</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>IBM Online Toastmasters Club</t>
+          <t>Philips Bangalore Toastmasters Club</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2305,17 +2305,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="9" t="n">
         <v>0</v>
@@ -2349,20 +2349,20 @@
       <c r="U17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="9" t="n">
-        <v>0</v>
+      <c r="V17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -2380,15 +2380,15 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>28675371</v>
+        <v>28679257</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Philips Bangalore Toastmasters Club</t>
+          <t>Sankalp Toastmasters Club</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2402,17 +2402,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="9" t="n">
         <v>0</v>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" s="9" t="n">
         <v>0</v>
@@ -2446,20 +2446,20 @@
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="10" t="n">
+      <c r="V18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="10" t="n">
-        <v>1</v>
+      <c r="Z18" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2640,11 +2640,11 @@
       <c r="U20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="9" t="n">
-        <v>3</v>
+      <c r="V20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>5</v>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2749,8 +2749,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>0</v>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5077,8 +5077,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6241,8 +6241,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6406,16 +6406,16 @@
         </is>
       </c>
       <c r="P59" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q59" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="Q59" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R59" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S59" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T59" s="10" t="n">
         <v>1</v>
@@ -6435,8 +6435,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>0</v>
@@ -6517,8 +6517,8 @@
       <c r="T60" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U60" s="9" t="n">
-        <v>0</v>
+      <c r="U60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V60" s="9" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -6987,11 +6987,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P65" s="9" t="n">
-        <v>2</v>
+      <c r="P65" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>0</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7114,8 +7114,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7479,7 +7479,7 @@
         <v>2</v>
       </c>
       <c r="R70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" s="9" t="n">
         <v>0</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7696,8 +7696,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
@@ -7872,8 +7872,8 @@
       <c r="S74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T74" s="9" t="n">
-        <v>0</v>
+      <c r="T74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U74" s="9" t="n">
         <v>0</v>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="P75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="9" t="n">
         <v>1</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8181,8 +8181,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8258,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" s="9" t="n">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8345,8 +8345,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P79" s="9" t="n">
-        <v>3</v>
+      <c r="P79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q79" s="10" t="n">
         <v>2</v>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8763,8 +8763,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q89" s="10" t="n">
         <v>2</v>
@@ -9525,7 +9525,7 @@
         <v>1</v>
       </c>
       <c r="U91" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V91" s="9" t="n">
         <v>0</v>
@@ -9849,15 +9849,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>5185978</v>
+        <v>28680949</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Electronics City Toastmasters Club</t>
+          <t>e-RISE Toastmasters</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,17 +9871,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -9898,16 +9898,16 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q95" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S95" s="10" t="n">
-        <v>2</v>
+      <c r="S95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T95" s="9" t="n">
         <v>0</v>
@@ -9915,14 +9915,14 @@
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="10" t="n">
-        <v>4</v>
+      <c r="V95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X95" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="X95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
@@ -9946,15 +9946,15 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>28677529</v>
+        <v>5185978</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>HPE Element Toastmasters</t>
+          <t>Electronics City Toastmasters Club</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -9995,16 +9995,16 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q96" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S96" s="9" t="n">
-        <v>0</v>
+      <c r="S96" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T96" s="9" t="n">
         <v>0</v>
@@ -10012,11 +10012,11 @@
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="9" t="n">
-        <v>0</v>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>7</v>
@@ -10024,8 +10024,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10043,15 +10043,15 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>4304110</v>
+        <v>28677529</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Siemens Bangalore Toastmasters Club</t>
+          <t>HPE Element Toastmasters</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -10110,19 +10110,19 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X97" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="10" t="n">
-        <v>1</v>
+      <c r="Z97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10140,15 +10140,15 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>28679397</v>
+        <v>4304110</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>TechM Bengaluru Toastmasters Club</t>
+          <t>Siemens Bangalore Toastmasters Club</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K98" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L98" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q98" s="9" t="n">
         <v>1</v>
@@ -10200,8 +10200,8 @@
       <c r="S98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T98" s="10" t="n">
-        <v>1</v>
+      <c r="T98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U98" s="9" t="n">
         <v>0</v>
@@ -10213,7 +10213,7 @@
         <v>0</v>
       </c>
       <c r="X98" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10233,19 +10233,19 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>3674956</v>
+        <v>28679397</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>CGI Elite Speakers Forum</t>
+          <t>TechM Bengaluru Toastmasters Club</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10259,17 +10259,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10286,7 +10286,7 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q99" s="9" t="n">
         <v>1</v>
@@ -10297,20 +10297,20 @@
       <c r="S99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T99" s="9" t="n">
-        <v>0</v>
+      <c r="T99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X99" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -10334,11 +10334,11 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>28677664</v>
+        <v>3674956</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Tessolve Toastmasters Club</t>
+          <t>CGI Elite Speakers Forum</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
@@ -10356,17 +10356,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L100" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -10383,10 +10383,10 @@
         </is>
       </c>
       <c r="P100" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R100" s="9" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="X100" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
@@ -10431,15 +10431,15 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>7641558</v>
+        <v>28677664</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Toast and Tales Toastmasters Club</t>
+          <t>Tessolve Toastmasters Club</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10453,17 +10453,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -10479,29 +10479,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P101" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q101" s="10" t="n">
+      <c r="P101" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="Q101" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S101" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T101" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U101" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="T101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W101" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>7</v>
@@ -10528,15 +10528,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>6975394</v>
+        <v>7641558</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters of HP</t>
+          <t>Toast and Tales Toastmasters Club</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -10576,12 +10576,12 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P102" s="9" t="n">
+      <c r="P102" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R102" s="9" t="n">
         <v>0</v>
       </c>
@@ -10591,14 +10591,14 @@
       <c r="T102" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" s="9" t="n">
-        <v>0</v>
+      <c r="U102" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V102" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>7</v>
@@ -10621,19 +10621,19 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>28677107</v>
+        <v>6975394</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Ascent Toastmasters Club</t>
+          <t>Toastmasters of HP</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K103" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L103" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -10674,19 +10674,19 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U103" s="9" t="n">
         <v>0</v>
@@ -10697,14 +10697,14 @@
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="9" t="n">
-        <v>1</v>
+      <c r="X103" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -10722,15 +10722,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>28678026</v>
+        <v>28677107</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Brighthearts Toastmasters</t>
+          <t>Ascent Toastmasters Club</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,17 +10744,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -10771,37 +10771,37 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q104" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T104" s="10" t="n">
-        <v>1</v>
+      <c r="T104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V104" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W104" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X104" s="10" t="n">
-        <v>7</v>
+      <c r="V104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="10" t="n">
-        <v>1</v>
+      <c r="Z104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -10819,15 +10819,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>28680911</v>
+        <v>28678026</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Paychex Catalyst Crew</t>
+          <t>Brighthearts Toastmasters</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -10868,37 +10868,37 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q105" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T105" s="9" t="n">
-        <v>0</v>
+      <c r="T105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X105" s="9" t="n">
-        <v>0</v>
+      <c r="V105" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W105" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X105" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z105" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -10916,15 +10916,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>28678996</v>
+        <v>28680911</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Paychex Catalyst Crew 1</t>
+          <t>Paychex Catalyst Crew</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10938,25 +10938,25 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K106" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L106" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N106" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O106" s="7" t="inlineStr">
@@ -10988,17 +10988,17 @@
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="9" t="n">
-        <v>0</v>
+      <c r="X106" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA106" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -11013,15 +11013,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>7908984</v>
+        <v>28678996</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>RCB Griffin</t>
+          <t>Paychex Catalyst Crew 1</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11035,25 +11035,25 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K107" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O107" s="7" t="inlineStr">
@@ -11062,22 +11062,22 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S107" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T107" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U107" s="10" t="n">
-        <v>3</v>
+      <c r="S107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
         <v>0</v>
@@ -11085,17 +11085,17 @@
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="10" t="n">
-        <v>7</v>
+      <c r="X107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA107" s="10" t="n">
-        <v>1</v>
+      <c r="Z107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -11110,15 +11110,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>7908988</v>
+        <v>7908984</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>RCB Pegasus</t>
+          <t>RCB Griffin</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11158,23 +11158,23 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P108" s="9" t="n">
+      <c r="P108" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q108" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q108" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="S108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T108" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U108" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V108" s="9" t="n">
         <v>0</v>
@@ -11207,15 +11207,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>7908991</v>
+        <v>7908988</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>RCB Phoenix</t>
+          <t>RCB Pegasus</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11229,25 +11229,25 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L109" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O109" s="7" t="inlineStr">
@@ -11256,22 +11256,22 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q109" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U109" s="9" t="n">
-        <v>0</v>
+      <c r="S109" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T109" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V109" s="9" t="n">
         <v>0</v>
@@ -11279,17 +11279,17 @@
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X109" s="9" t="n">
-        <v>0</v>
+      <c r="X109" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA109" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -11300,19 +11300,19 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>28675609</v>
+        <v>7908991</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Greenage Toastmasters Club</t>
+          <t>RCB Phoenix</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11326,25 +11326,25 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N110" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O110" s="7" t="inlineStr">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>0</v>
@@ -11371,22 +11371,22 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X110" s="10" t="n">
-        <v>5</v>
+      <c r="X110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA110" s="10" t="n">
-        <v>1</v>
+      <c r="Z110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -11401,15 +11401,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>5843852</v>
+        <v>28675609</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>HSR Toastmasters Club</t>
+          <t>Greenage Toastmasters Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11452,29 +11452,29 @@
       <c r="P111" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q111" s="10" t="n">
+      <c r="Q111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T111" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V111" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="W111" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X111" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -11498,15 +11498,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>9688</v>
+        <v>5843852</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Infosys Toastmasters, Bangalore</t>
+          <t>HSR Toastmasters Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -11549,8 +11549,8 @@
       <c r="P112" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q112" s="9" t="n">
-        <v>0</v>
+      <c r="Q112" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -11558,17 +11558,17 @@
       <c r="S112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" s="9" t="n">
-        <v>0</v>
+      <c r="T112" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V112" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>7</v>
@@ -11595,11 +11595,11 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>7586759</v>
+        <v>9688</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>MOOG Flyers</t>
+          <t>Infosys Toastmasters, Bangalore</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -11620,10 +11620,10 @@
         <v>29</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -11655,20 +11655,20 @@
       <c r="S113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T113" s="10" t="n">
-        <v>1</v>
+      <c r="T113" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>0</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -11692,15 +11692,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>7959873</v>
+        <v>7586759</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Wipro House of Speakers</t>
+          <t>MOOG Flyers</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11714,17 +11714,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L114" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -11741,7 +11741,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -11749,29 +11749,29 @@
       <c r="R114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S114" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T114" s="9" t="n">
-        <v>0</v>
+      <c r="S114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X114" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
@@ -11780,24 +11780,24 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>28679896</v>
+        <v>28681022</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Chilli Champions Toastmasters Club</t>
+          <t>SpeakUp Scaler Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -11867,8 +11867,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -11877,20 +11877,20 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>4184180</v>
+        <v>7959873</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Deshpande Educational Trust Toastmasters Club</t>
+          <t>Wipro House of Speakers</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
@@ -11908,17 +11908,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>0</v>
@@ -11943,8 +11943,8 @@
       <c r="R116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S116" s="9" t="n">
-        <v>0</v>
+      <c r="S116" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T116" s="9" t="n">
         <v>0</v>
@@ -11953,19 +11953,19 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="10" t="n">
-        <v>1</v>
+      <c r="Z116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -11983,15 +11983,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>28678921</v>
+        <v>28679896</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>InfyHubliVox Toastmasters Club</t>
+          <t>Chilli Champions Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,17 +12005,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K117" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L117" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12032,22 +12032,22 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q117" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U117" s="10" t="n">
-        <v>2</v>
+      <c r="T117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
         <v>0</v>
@@ -12055,8 +12055,8 @@
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X117" s="10" t="n">
-        <v>4</v>
+      <c r="X117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12080,15 +12080,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>6988591</v>
+        <v>4184180</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>SDMCET Toastmasters Club</t>
+          <t>Deshpande Educational Trust Toastmasters Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,17 +12102,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q118" s="9" t="n">
         <v>0</v>
@@ -12147,19 +12147,19 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X118" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -12177,15 +12177,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>7712481</v>
+        <v>28678921</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters For Hubballi Entrepreneurs</t>
+          <t>InfyHubliVox Toastmasters Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,17 +12199,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -12226,37 +12226,37 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q119" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S119" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U119" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W119" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X119" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="10" t="n">
-        <v>1</v>
+      <c r="Z119" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -12270,19 +12270,19 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>28675688</v>
+        <v>6988591</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>APS Toastmasters Club</t>
+          <t>SDMCET Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,17 +12296,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
@@ -12323,37 +12323,37 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S120" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T120" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="10" t="n">
-        <v>1</v>
+      <c r="Z120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -12367,19 +12367,19 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>28677946</v>
+        <v>7712481</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Belagavi Toastmasters Centenary Club</t>
+          <t>Toastmasters For Hubballi Entrepreneurs</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q121" s="10" t="n">
         <v>2</v>
@@ -12431,17 +12431,17 @@
       <c r="S121" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T121" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U121" s="10" t="n">
-        <v>2</v>
+      <c r="T121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V121" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W121" s="9" t="n">
-        <v>1</v>
+      <c r="W121" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X121" s="10" t="n">
         <v>7</v>
@@ -12468,15 +12468,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>7826939</v>
+        <v>28675688</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Kannada English Bilingual Toastmasters Club</t>
+          <t>APS Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12490,17 +12490,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M122" s="8" t="n">
@@ -12516,11 +12516,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P122" s="9" t="n">
-        <v>2</v>
+      <c r="P122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
@@ -12531,17 +12531,17 @@
       <c r="T122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U122" s="9" t="n">
-        <v>0</v>
+      <c r="U122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X122" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -12565,15 +12565,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>6997339</v>
+        <v>28677946</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>KLS IMER Toastmasters</t>
+          <t>Belagavi Toastmasters Centenary Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K123" s="4" t="n">
         <v>5</v>
@@ -12614,10 +12614,10 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q123" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q123" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
@@ -12625,11 +12625,11 @@
       <c r="S123" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" s="9" t="n">
-        <v>0</v>
+      <c r="T123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U123" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V123" s="10" t="n">
         <v>4</v>
@@ -12638,7 +12638,7 @@
         <v>1</v>
       </c>
       <c r="X123" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -12662,15 +12662,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>7335393</v>
+        <v>7826939</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Shivamogga Toastmasters</t>
+          <t>Kannada English Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,10 +12684,10 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K124" s="4" t="n">
         <v>0</v>
@@ -12698,11 +12698,11 @@
         </is>
       </c>
       <c r="M124" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O124" s="7" t="inlineStr">
@@ -12711,7 +12711,7 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
@@ -12720,10 +12720,10 @@
         <v>0</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U124" s="9" t="n">
         <v>0</v>
@@ -12734,17 +12734,17 @@
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="9" t="n">
-        <v>0</v>
+      <c r="X124" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA124" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -12759,15 +12759,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>28680663</v>
+        <v>6997339</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>SPS Toastmasters Club</t>
+          <t>KLS IMER Toastmasters</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>0</v>
@@ -12817,7 +12817,7 @@
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T125" s="9" t="n">
         <v>0</v>
@@ -12825,20 +12825,20 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>0</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -12852,19 +12852,19 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>1214543</v>
+        <v>7335393</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>GOA Toastmasters Club</t>
+          <t>Shivamogga Toastmasters</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,25 +12878,25 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="K126" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N126" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O126" s="7" t="inlineStr">
@@ -12905,16 +12905,16 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T126" s="9" t="n">
         <v>0</v>
@@ -12928,17 +12928,17 @@
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X126" s="10" t="n">
-        <v>7</v>
+      <c r="X126" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA126" s="10" t="n">
-        <v>1</v>
+      <c r="Z126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -12949,15 +12949,15 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>3214306</v>
+        <v>28680663</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>International Centre GOA (ICG) Toastmasters Club</t>
+          <t>SPS Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13002,10 +13002,10 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13020,13 +13020,13 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X127" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13050,11 +13050,11 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>28676711</v>
+        <v>1214543</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Melange Toastmasters Club</t>
+          <t>GOA Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
@@ -13072,17 +13072,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L128" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
@@ -13099,7 +13099,7 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q128" s="9" t="n">
         <v>1</v>
@@ -13108,7 +13108,7 @@
         <v>0</v>
       </c>
       <c r="S128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" s="9" t="n">
         <v>0</v>
@@ -13117,7 +13117,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13147,11 +13147,11 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>7946347</v>
+        <v>3214306</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>TheanTamil Toastmasters Club</t>
+          <t>International Centre GOA (ICG) Toastmasters Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -13169,17 +13169,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L129" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13196,10 +13196,10 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R129" s="9" t="n">
         <v>0</v>
@@ -13214,13 +13214,13 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X129" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -13244,11 +13244,11 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>2575847</v>
+        <v>28676711</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters International Margao</t>
+          <t>Melange Toastmasters Club</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>1</v>
@@ -13296,7 +13296,7 @@
         <v>0</v>
       </c>
       <c r="Q130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R130" s="9" t="n">
         <v>0</v>
@@ -13317,7 +13317,7 @@
         <v>0</v>
       </c>
       <c r="X130" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
@@ -13337,15 +13337,15 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>28678487</v>
+        <v>7946347</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Calangute Toastmasters Club</t>
+          <t>TheanTamil Toastmasters Club</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -13363,17 +13363,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M131" s="8" t="n">
@@ -13390,10 +13390,10 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>0</v>
@@ -13408,13 +13408,13 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X131" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -13434,15 +13434,15 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>4361333</v>
+        <v>2575847</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Mapusa Toastmasters</t>
+          <t>Toastmasters International Margao</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K132" s="4" t="n">
         <v>1</v>
@@ -13496,10 +13496,10 @@
         <v>0</v>
       </c>
       <c r="S132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T132" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T132" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U132" s="9" t="n">
         <v>0</v>
@@ -13511,13 +13511,13 @@
         <v>0</v>
       </c>
       <c r="X132" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -13535,15 +13535,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>7856600</v>
+        <v>28678487</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Online Toastmasters Tribe</t>
+          <t>Calangute Toastmasters Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,17 +13557,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M133" s="8" t="n">
@@ -13584,10 +13584,10 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -13602,19 +13602,19 @@
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X133" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -13632,15 +13632,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>6941455</v>
+        <v>4361333</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Tangentia Toastmasters</t>
+          <t>Mapusa Toastmasters</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -13690,28 +13690,28 @@
         <v>0</v>
       </c>
       <c r="S134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X134" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -13720,24 +13720,24 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>632425</v>
+        <v>7856600</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>CMS Speakers Forum Toastmasters Club</t>
+          <t>Online Toastmasters Tribe</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -13778,37 +13778,37 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q135" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q135" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R135" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S135" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T135" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U135" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="S135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -13817,24 +13817,24 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>725960</v>
+        <v>6941455</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Jain Toastmasters Club</t>
+          <t>Tangentia Toastmasters</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -13875,37 +13875,37 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q136" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S136" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T136" s="10" t="n">
-        <v>1</v>
+      <c r="S136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X136" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -13923,15 +13923,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>726698</v>
+        <v>632425</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Mahaveer Toastmasters Club</t>
+          <t>CMS Speakers Forum Toastmasters Club</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -13986,11 +13986,11 @@
       <c r="T137" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U137" s="9" t="n">
-        <v>0</v>
+      <c r="U137" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
@@ -14020,15 +14020,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>726395</v>
+        <v>725960</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>SBMJC Toastmasters Club</t>
+          <t>Jain Toastmasters Club</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14068,23 +14068,23 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P138" s="10" t="n">
-        <v>5</v>
+      <c r="P138" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Q138" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R138" s="10" t="n">
-        <v>3</v>
+      <c r="R138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S138" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T138" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U138" s="10" t="n">
-        <v>2</v>
+      <c r="U138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
         <v>2</v>
@@ -14113,19 +14113,19 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>6636162</v>
+        <v>726698</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>BTM Toastmasters Club</t>
+          <t>Mahaveer Toastmasters Club</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14139,17 +14139,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -14166,16 +14166,16 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q139" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="S139" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T139" s="10" t="n">
         <v>1</v>
@@ -14183,11 +14183,11 @@
       <c r="U139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V139" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W139" s="10" t="n">
-        <v>4</v>
+      <c r="V139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X139" s="10" t="n">
         <v>7</v>
@@ -14195,8 +14195,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="10" t="n">
-        <v>1</v>
+      <c r="Z139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -14210,19 +14210,19 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>28678910</v>
+        <v>726395</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Furlenco Toastmasters Club</t>
+          <t>SBMJC Toastmasters Club</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14262,32 +14262,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" s="9" t="n">
-        <v>0</v>
+      <c r="P140" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q140" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R140" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S140" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U140" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X140" s="9" t="n">
-        <v>2</v>
+      <c r="X140" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
@@ -14311,15 +14311,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>6831114</v>
+        <v>6636162</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Leaders Speak</t>
+          <t>BTM Toastmasters Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -14360,16 +14360,16 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q141" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q141" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T141" s="10" t="n">
         <v>1</v>
@@ -14377,14 +14377,14 @@
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W141" s="9" t="n">
-        <v>0</v>
+      <c r="V141" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W141" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X141" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
@@ -14408,11 +14408,11 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>2405453</v>
+        <v>28678910</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>vTalk Toastmasters Club</t>
+          <t>Furlenco Toastmasters Club</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -14475,13 +14475,13 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X142" s="10" t="n">
-        <v>4</v>
+      <c r="X142" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
@@ -14505,11 +14505,11 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>28678951</v>
+        <v>6831114</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Welldoc Toastmasters</t>
+          <t>Leaders Speak</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -14553,8 +14553,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P143" s="9" t="n">
-        <v>0</v>
+      <c r="P143" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q143" s="9" t="n">
         <v>0</v>
@@ -14565,20 +14565,20 @@
       <c r="S143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T143" s="9" t="n">
-        <v>0</v>
+      <c r="T143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V143" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W143" s="10" t="n">
-        <v>9</v>
+      <c r="V143" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X143" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
@@ -14598,19 +14598,19 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>7762021</v>
+        <v>2405453</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Christ Toastmasters Club</t>
+          <t>vTalk Toastmasters Club</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,17 +14624,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M144" s="8" t="n">
@@ -14662,20 +14662,20 @@
       <c r="S144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T144" s="10" t="n">
-        <v>1</v>
+      <c r="T144" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="10" t="n">
+      <c r="V144" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="W144" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="X144" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
@@ -14695,19 +14695,19 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>28678938</v>
+        <v>28678951</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>DSBA Toastmaster Club</t>
+          <t>Welldoc Toastmasters</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
@@ -14747,29 +14747,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P145" s="10" t="n">
+      <c r="P145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W145" s="9" t="n">
-        <v>0</v>
+      <c r="W145" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X145" s="10" t="n">
         <v>7</v>
@@ -14777,8 +14777,8 @@
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -14796,15 +14796,15 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>28679826</v>
+        <v>7762021</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>DSBA Toastmasters Legacy Club</t>
+          <t>Christ Toastmasters Club</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         </is>
       </c>
       <c r="P146" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q146" s="9" t="n">
         <v>0</v>
@@ -14856,17 +14856,17 @@
       <c r="S146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T146" s="9" t="n">
-        <v>0</v>
+      <c r="T146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W146" s="9" t="n">
-        <v>0</v>
+      <c r="V146" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W146" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X146" s="10" t="n">
         <v>7</v>
@@ -14874,8 +14874,8 @@
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
@@ -14893,15 +14893,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>28676701</v>
+        <v>28678938</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Evolve Toastmasters</t>
+          <t>DSBA Toastmaster Club</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14915,10 +14915,10 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K147" s="4" t="n">
         <v>0</v>
@@ -14941,8 +14941,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P147" s="9" t="n">
-        <v>0</v>
+      <c r="P147" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q147" s="9" t="n">
         <v>0</v>
@@ -14990,15 +14990,15 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>7711039</v>
+        <v>28679826</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Words Worth Toastmasters</t>
+          <t>DSBA Toastmasters Legacy Club</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
@@ -15039,16 +15039,16 @@
         </is>
       </c>
       <c r="P148" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q148" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S148" s="10" t="n">
-        <v>2</v>
+      <c r="S148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T148" s="9" t="n">
         <v>0</v>
@@ -15056,11 +15056,11 @@
       <c r="U148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V148" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W148" s="10" t="n">
-        <v>10</v>
+      <c r="V148" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X148" s="10" t="n">
         <v>7</v>
@@ -15068,8 +15068,8 @@
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="10" t="n">
-        <v>1</v>
+      <c r="Z148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA148" s="10" t="n">
         <v>1</v>
@@ -15083,15 +15083,15 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>7992645</v>
+        <v>28676701</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>All Women and Entrepreneurs Toastmasters Club</t>
+          <t>Evolve Toastmasters</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
@@ -15109,10 +15109,10 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K149" s="4" t="n">
         <v>0</v>
@@ -15160,7 +15160,7 @@
         <v>0</v>
       </c>
       <c r="X149" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
@@ -15180,19 +15180,19 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>5953659</v>
+        <v>7711039</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Ritoras</t>
+          <t>Words Worth Toastmasters</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q150" s="9" t="n">
         <v>1</v>
@@ -15241,8 +15241,8 @@
       <c r="R150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S150" s="9" t="n">
-        <v>1</v>
+      <c r="S150" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T150" s="9" t="n">
         <v>0</v>
@@ -15250,11 +15250,11 @@
       <c r="U150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V150" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W150" s="9" t="n">
-        <v>0</v>
+      <c r="V150" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W150" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>7</v>
@@ -15281,15 +15281,15 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>28675687</v>
+        <v>7992645</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>School of Commerce, Jain University Toastmasters</t>
+          <t>All Women and Entrepreneurs Toastmasters Club</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
@@ -15330,10 +15330,10 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q151" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>0</v>
@@ -15347,20 +15347,20 @@
       <c r="U151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V151" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W151" s="10" t="n">
-        <v>6</v>
+      <c r="V151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X151" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="10" t="n">
-        <v>1</v>
+      <c r="Z151" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA151" s="10" t="n">
         <v>1</v>
@@ -15378,11 +15378,11 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>7934414</v>
+        <v>5953659</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>SpeakEasy Advanced Toastmasters</t>
+          <t>Ritoras</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J152" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J152" s="4" t="n">
-        <v>20</v>
-      </c>
       <c r="K152" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -15430,34 +15430,34 @@
         <v>0</v>
       </c>
       <c r="Q152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T152" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T152" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X152" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z152" s="9" t="n">
-        <v>0</v>
+      <c r="Z152" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA152" s="10" t="n">
         <v>1</v>
@@ -15475,15 +15475,15 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>28677183</v>
+        <v>28675687</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Titans Toastmasters Club</t>
+          <t>School of Commerce, Jain University Toastmasters</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -15524,10 +15524,10 @@
         </is>
       </c>
       <c r="P153" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R153" s="9" t="n">
         <v>0</v>
@@ -15544,8 +15544,8 @@
       <c r="V153" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W153" s="9" t="n">
-        <v>3</v>
+      <c r="W153" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X153" s="10" t="n">
         <v>7</v>
@@ -15560,8 +15560,202 @@
         <v>1</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="n">
+        <v>7934414</v>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>SpeakEasy Advanced Toastmasters</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G154" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J154" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K154" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M154" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N154" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O154" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA154" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="n">
+        <v>28677183</v>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>Titans Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G155" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J155" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K155" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M155" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N155" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O155" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W155" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="X155" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA155" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA153"/>
+  <autoFilter ref="A1:AA155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15681,13 +15875,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -15747,7 +15941,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15879,7 +16073,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15945,13 +16139,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -15978,7 +16172,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -16011,7 +16205,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16044,7 +16238,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16077,7 +16271,7 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -16173,16 +16367,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -16242,13 +16436,13 @@
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>1.86</v>
+        <v>2.43</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -16272,13 +16466,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>5</v>
@@ -16290,7 +16484,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -16341,7 +16535,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -16407,7 +16601,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16473,7 +16667,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -16539,7 +16733,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/227/inyear.xlsx
+++ b/docs/d/227/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 50 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 49 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1167,11 +1167,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="9" t="n">
-        <v>0</v>
+      <c r="P5" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R5" s="9" t="n">
         <v>0</v>
@@ -1188,8 +1188,8 @@
       <c r="V5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W5" s="9" t="n">
-        <v>3</v>
+      <c r="W5" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>7</v>
@@ -1238,17 +1238,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1283,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1335,17 +1335,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M7" s="8" t="n">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5</v>
+        <v>-12</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>4</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>7</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1626,17 +1626,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M10" s="8" t="n">
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1723,17 +1723,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1755,8 +1755,8 @@
       <c r="Q11" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R11" s="9" t="n">
-        <v>0</v>
+      <c r="R11" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S11" s="9" t="n">
         <v>0</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1917,17 +1917,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M13" s="8" t="n">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="P13" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q13" s="10" t="n">
         <v>2</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2058,11 +2058,11 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W14" s="9" t="n">
-        <v>0</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>7</v>
@@ -2208,17 +2208,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2331,8 +2331,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P17" s="9" t="n">
-        <v>3</v>
+      <c r="P17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2596,17 +2596,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2644,7 +2644,7 @@
         <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>5</v>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2790,17 +2790,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>50</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-50</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -2887,17 +2887,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>7</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3119,14 +3119,14 @@
       <c r="S25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T25" s="9" t="n">
-        <v>0</v>
+      <c r="T25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3222,8 +3222,8 @@
       <c r="U26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="9" t="n">
-        <v>3</v>
+      <c r="V26" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3304,8 +3304,8 @@
       <c r="P27" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q27" s="9" t="n">
-        <v>1</v>
+      <c r="Q27" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -3316,14 +3316,14 @@
       <c r="T27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U27" s="9" t="n">
-        <v>0</v>
+      <c r="U27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V27" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W27" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>7</v>
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>72</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3689,8 +3689,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P31" s="9" t="n">
-        <v>3</v>
+      <c r="P31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>1</v>
@@ -3710,8 +3710,8 @@
       <c r="V31" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W31" s="9" t="n">
-        <v>3</v>
+      <c r="W31" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>7</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4483,8 +4483,8 @@
       <c r="U39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="9" t="n">
-        <v>3</v>
+      <c r="V39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4633,17 +4633,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M41" s="8" t="n">
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4827,17 +4827,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -4871,8 +4871,8 @@
       <c r="U43" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>2</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X44" s="10" t="n">
         <v>7</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5162,11 +5162,11 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>1</v>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>5</v>
@@ -5215,17 +5215,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M47" s="8" t="n">
@@ -5312,17 +5312,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="8" t="n">
@@ -5409,17 +5409,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>68</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-68</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>4</v>
       </c>
       <c r="W54" s="10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>7</v>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6185,17 +6185,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6282,17 +6282,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6423,11 +6423,11 @@
       <c r="U59" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" s="9" t="n">
-        <v>0</v>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W59" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>7</v>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6573,17 +6573,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-35</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>9</v>
+        <v>-3</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>4</v>
       </c>
       <c r="W62" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>7</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>55</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>4</v>
       </c>
       <c r="W64" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X64" s="10" t="n">
         <v>7</v>
@@ -6961,17 +6961,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-37</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>59</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7202,8 +7202,8 @@
       <c r="V67" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W67" s="9" t="n">
-        <v>0</v>
+      <c r="W67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X67" s="10" t="n">
         <v>7</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7349,17 +7349,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7490,11 +7490,11 @@
       <c r="U70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" s="9" t="n">
-        <v>0</v>
+      <c r="V70" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W70" s="10" t="n">
+        <v>19</v>
       </c>
       <c r="X70" s="10" t="n">
         <v>5</v>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>83</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>-37</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7587,11 +7587,11 @@
       <c r="U71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" s="9" t="n">
-        <v>0</v>
+      <c r="V71" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W71" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>7</v>
@@ -7640,17 +7640,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M72" s="8" t="n">
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -7931,17 +7931,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8169,11 +8169,11 @@
       <c r="U77" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" s="9" t="n">
-        <v>0</v>
+      <c r="V77" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W77" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>6</v>
@@ -8222,17 +8222,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8267,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>4</v>
       </c>
       <c r="W79" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>7</v>
@@ -8513,17 +8513,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8707,17 +8707,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -8751,11 +8751,11 @@
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" s="9" t="n">
-        <v>0</v>
+      <c r="V83" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W83" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>4</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>5</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9042,8 +9042,8 @@
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>2</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>4</v>
       </c>
       <c r="W88" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>7</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>1</v>
       </c>
       <c r="U89" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V89" s="9" t="n">
         <v>2</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9483,17 +9483,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -9580,17 +9580,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -9677,17 +9677,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9871,17 +9871,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L95" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -9995,16 +9995,16 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q96" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R96" s="9" t="n">
-        <v>0</v>
+      <c r="R96" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S96" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T96" s="9" t="n">
         <v>0</v>
@@ -10065,17 +10065,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-45</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10188,8 +10188,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P98" s="9" t="n">
-        <v>3</v>
+      <c r="P98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q98" s="9" t="n">
         <v>1</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10400,11 +10400,11 @@
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="9" t="n">
-        <v>0</v>
+      <c r="V100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>6</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10497,11 +10497,11 @@
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="9" t="n">
-        <v>0</v>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>7</v>
@@ -10550,17 +10550,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -10583,7 +10583,7 @@
         <v>2</v>
       </c>
       <c r="R102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S102" s="9" t="n">
         <v>1</v>
@@ -10598,7 +10598,7 @@
         <v>4</v>
       </c>
       <c r="W102" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -10691,11 +10691,11 @@
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="9" t="n">
-        <v>0</v>
+      <c r="V103" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>7</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11159,13 +11159,13 @@
         </is>
       </c>
       <c r="P108" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q108" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R108" s="9" t="n">
-        <v>1</v>
+      <c r="R108" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="S108" s="10" t="n">
         <v>2</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11423,17 +11423,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T112" s="10" t="n">
         <v>1</v>
@@ -11567,8 +11567,8 @@
       <c r="V112" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W112" s="9" t="n">
-        <v>3</v>
+      <c r="W112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>7</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -11665,7 +11665,7 @@
         <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X113" s="10" t="n">
         <v>7</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J115" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="J115" s="4" t="n">
-        <v>20</v>
-      </c>
       <c r="K115" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -11952,11 +11952,11 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>2</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>4</v>
@@ -12005,17 +12005,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12102,17 +12102,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>4</v>
       </c>
       <c r="W121" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X121" s="10" t="n">
         <v>7</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -12534,8 +12534,8 @@
       <c r="U122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V122" s="9" t="n">
-        <v>3</v>
+      <c r="V122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -12587,17 +12587,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
@@ -12629,7 +12629,7 @@
         <v>1</v>
       </c>
       <c r="U123" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V123" s="10" t="n">
         <v>4</v>
@@ -12781,17 +12781,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>0</v>
       </c>
       <c r="S129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T129" s="9" t="n">
         <v>0</v>
@@ -13213,8 +13213,8 @@
       <c r="U129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="9" t="n">
-        <v>2</v>
+      <c r="V129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>0</v>
       </c>
       <c r="Q132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R132" s="9" t="n">
         <v>0</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -13893,7 +13893,7 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -14527,17 +14527,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -14668,8 +14668,8 @@
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="9" t="n">
-        <v>3</v>
+      <c r="V144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>4</v>
       </c>
       <c r="W146" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X146" s="10" t="n">
         <v>7</v>
@@ -14901,7 +14901,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -14959,11 +14959,11 @@
       <c r="U147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W147" s="9" t="n">
-        <v>0</v>
+      <c r="V147" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W147" s="10" t="n">
+        <v>21</v>
       </c>
       <c r="X147" s="10" t="n">
         <v>7</v>
@@ -14971,8 +14971,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -15012,17 +15012,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-26</v>
+      </c>
+      <c r="L148" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="8" t="n">
@@ -15109,17 +15109,17 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-33</v>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M149" s="8" t="n">
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15303,17 +15303,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L151" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M151" s="8" t="n">
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>4</v>
       </c>
       <c r="W153" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X153" s="10" t="n">
         <v>7</v>
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15594,17 +15594,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="8" t="n">
@@ -15638,11 +15638,11 @@
       <c r="U154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V154" s="9" t="n">
-        <v>3</v>
+      <c r="V154" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W154" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X154" s="10" t="n">
         <v>4</v>
@@ -15842,13 +15842,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -15857,7 +15857,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -15875,7 +15875,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -15890,7 +15890,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -15908,7 +15908,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -15923,7 +15923,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -15956,7 +15956,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -15974,7 +15974,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -15989,7 +15989,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -16007,13 +16007,13 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16055,7 +16055,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -16073,7 +16073,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16088,7 +16088,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -16139,7 +16139,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -16154,7 +16154,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -16187,7 +16187,7 @@
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -16205,13 +16205,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -16220,7 +16220,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -16238,13 +16238,13 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -16253,7 +16253,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -16271,13 +16271,13 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -16286,7 +16286,7 @@
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -16304,7 +16304,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16352,7 +16352,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -16370,13 +16370,13 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -16385,7 +16385,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -16403,7 +16403,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -16418,7 +16418,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -16436,7 +16436,7 @@
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
@@ -16469,7 +16469,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -16484,7 +16484,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -16517,7 +16517,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -16535,13 +16535,13 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -16550,7 +16550,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -16568,7 +16568,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -16682,7 +16682,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -16700,7 +16700,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16715,7 +16715,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -16733,7 +16733,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -16748,7 +16748,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/227/inyear.xlsx
+++ b/docs/d/227/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/227/inyear.xlsx
+++ b/docs/d/227/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/227/inyear.xlsx
+++ b/docs/d/227/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/227/inyear.xlsx
+++ b/docs/d/227/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/227/inyear.xlsx
+++ b/docs/d/227/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 49 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 49 clubs short</t>
         </is>
       </c>
     </row>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>4</v>
       </c>
       <c r="W5" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>7</v>
@@ -1465,7 +1465,7 @@
         <v>2</v>
       </c>
       <c r="R8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="9" t="n">
         <v>0</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3013,14 +3013,14 @@
       <c r="P24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" s="9" t="n">
-        <v>1</v>
+      <c r="Q24" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" s="10" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>2</v>
       </c>
       <c r="R27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U27" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="10" t="n">
         <v>4</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4580,11 +4580,11 @@
       <c r="U40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V40" s="9" t="n">
-        <v>1</v>
+      <c r="V40" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W40" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" s="10" t="n">
         <v>7</v>
@@ -4827,17 +4827,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5409,17 +5409,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>68</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-68</v>
-      </c>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-29</v>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5453,11 +5453,11 @@
       <c r="U49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" s="9" t="n">
-        <v>0</v>
+      <c r="V49" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W49" s="10" t="n">
+        <v>18</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>5</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6282,17 +6282,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L58" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6329,8 +6329,8 @@
       <c r="V58" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W58" s="9" t="n">
-        <v>3</v>
+      <c r="W58" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X58" s="10" t="n">
         <v>7</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>59</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>4</v>
       </c>
       <c r="W67" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X67" s="10" t="n">
         <v>7</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7296,11 +7296,11 @@
       <c r="U68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="9" t="n">
-        <v>2</v>
+      <c r="V68" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X68" s="10" t="n">
         <v>4</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>83</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-37</v>
+        <v>-36</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>4</v>
       </c>
       <c r="W71" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>7</v>
@@ -8152,7 +8152,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>0</v>
@@ -8355,7 +8355,7 @@
         <v>1</v>
       </c>
       <c r="S79" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T79" s="10" t="n">
         <v>1</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9039,14 +9039,14 @@
       <c r="T86" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U86" s="9" t="n">
-        <v>0</v>
+      <c r="U86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>7</v>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9512,8 +9512,8 @@
       <c r="P91" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q91" s="9" t="n">
-        <v>1</v>
+      <c r="Q91" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -9909,14 +9909,14 @@
       <c r="S95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T95" s="9" t="n">
-        <v>0</v>
+      <c r="T95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10582,8 +10582,8 @@
       <c r="Q102" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R102" s="9" t="n">
-        <v>1</v>
+      <c r="R102" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S102" s="9" t="n">
         <v>1</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>4</v>
       </c>
       <c r="W103" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>7</v>
@@ -11165,7 +11165,7 @@
         <v>2</v>
       </c>
       <c r="R108" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S108" s="10" t="n">
         <v>2</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>4</v>
       </c>
       <c r="W112" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>7</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11643,8 +11643,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P113" s="9" t="n">
-        <v>3</v>
+      <c r="P113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q118" s="9" t="n">
         <v>0</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12819,8 +12819,8 @@
       <c r="S125" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T125" s="9" t="n">
-        <v>0</v>
+      <c r="T125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U125" s="9" t="n">
         <v>0</v>
@@ -13446,7 +13446,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13487,10 +13487,10 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q132" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R132" s="9" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14759,8 +14759,8 @@
       <c r="S145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T145" s="9" t="n">
-        <v>0</v>
+      <c r="T145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U145" s="9" t="n">
         <v>0</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>-26</v>
+        <v>-24</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>4</v>
       </c>
       <c r="W150" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>7</v>
@@ -15941,7 +15941,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16055,7 +16055,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -16073,13 +16073,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -16088,7 +16088,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -16139,7 +16139,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>3.17</v>
+        <v>3.33</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -16154,7 +16154,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -16205,7 +16205,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -16304,7 +16304,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16337,7 +16337,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -16370,7 +16370,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -16403,7 +16403,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -16469,7 +16469,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -16535,7 +16535,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -16568,7 +16568,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>

--- a/docs/d/227/inyear.xlsx
+++ b/docs/d/227/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 49 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 49 clubs short</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>1</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>4</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" s="10" t="n">
         <v>5</v>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>4</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>7</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2043,8 +2043,8 @@
       <c r="P14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" s="9" t="n">
-        <v>1</v>
+      <c r="Q14" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="9" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2916,8 +2916,8 @@
       <c r="P23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="9" t="n">
-        <v>1</v>
+      <c r="Q23" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R23" s="9" t="n">
         <v>0</v>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3025,8 +3025,8 @@
       <c r="T24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U24" s="9" t="n">
-        <v>0</v>
+      <c r="U24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V24" s="10" t="n">
         <v>4</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3504,8 +3504,8 @@
       <c r="R29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="9" t="n">
-        <v>1</v>
+      <c r="S29" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T29" s="10" t="n">
         <v>1</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>0</v>
@@ -3901,11 +3901,11 @@
       <c r="U33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="9" t="n">
-        <v>0</v>
+      <c r="V33" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W33" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X33" s="10" t="n">
         <v>5</v>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="P37" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="9" t="n">
         <v>0</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4583,8 +4583,8 @@
       <c r="V40" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W40" s="9" t="n">
-        <v>2</v>
+      <c r="W40" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X40" s="10" t="n">
         <v>7</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4853,8 +4853,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P43" s="9" t="n">
-        <v>3</v>
+      <c r="P43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q43" s="9" t="n">
         <v>0</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -4959,8 +4959,8 @@
       <c r="R44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S44" s="9" t="n">
-        <v>0</v>
+      <c r="S44" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T44" s="9" t="n">
         <v>0</v>
@@ -5215,17 +5215,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M47" s="8" t="n">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>68</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>4</v>
       </c>
       <c r="W49" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>5</v>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>1</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7478,8 +7478,8 @@
       <c r="Q70" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R70" s="9" t="n">
-        <v>1</v>
+      <c r="R70" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S70" s="9" t="n">
         <v>0</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>83</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-36</v>
+        <v>-35</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>4</v>
       </c>
       <c r="W71" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>7</v>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>4</v>
       </c>
       <c r="W74" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>7</v>
@@ -8152,7 +8152,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>0</v>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8927,8 +8927,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P85" s="9" t="n">
-        <v>3</v>
+      <c r="P85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q85" s="10" t="n">
         <v>2</v>
@@ -8939,8 +8939,8 @@
       <c r="S85" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9233,8 +9233,8 @@
       <c r="T88" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U88" s="9" t="n">
-        <v>0</v>
+      <c r="U88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V88" s="10" t="n">
         <v>4</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,17 +10065,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-45</v>
-      </c>
-      <c r="L97" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>13</v>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10091,11 +10091,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P97" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q97" s="9" t="n">
-        <v>0</v>
+      <c r="P97" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q97" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -10103,17 +10103,17 @@
       <c r="S97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T97" s="9" t="n">
-        <v>0</v>
+      <c r="T97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" s="9" t="n">
-        <v>0</v>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W97" s="10" t="n">
+        <v>21</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>7</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11555,14 +11555,14 @@
       <c r="R112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S112" s="9" t="n">
-        <v>1</v>
+      <c r="S112" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T112" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U112" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V112" s="10" t="n">
         <v>4</v>
@@ -13058,7 +13058,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q128" s="9" t="n">
         <v>1</v>
@@ -13116,8 +13116,8 @@
       <c r="U128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="9" t="n">
-        <v>3</v>
+      <c r="V128" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -14359,8 +14359,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P141" s="9" t="n">
-        <v>2</v>
+      <c r="P141" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q141" s="10" t="n">
         <v>2</v>
@@ -14804,7 +14804,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -14854,13 +14854,13 @@
         <v>0</v>
       </c>
       <c r="S146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T146" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U146" s="9" t="n">
-        <v>0</v>
+      <c r="U146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V146" s="10" t="n">
         <v>4</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15244,8 +15244,8 @@
       <c r="S150" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T150" s="9" t="n">
-        <v>0</v>
+      <c r="T150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U150" s="9" t="n">
         <v>0</v>
@@ -15908,7 +15908,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -15941,13 +15941,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -16007,7 +16007,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>2.14</v>
+        <v>2.43</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -16040,13 +16040,13 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -16073,7 +16073,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -16088,7 +16088,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -16238,7 +16238,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -16304,13 +16304,13 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -16370,13 +16370,13 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -16385,7 +16385,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -16469,7 +16469,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -16568,7 +16568,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -16700,13 +16700,13 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
